--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260713.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.51%</t>
+          <t>10.85%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.97%</t>
+          <t>8.87%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.22%</t>
+          <t>7.61%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.33%</t>
+          <t>7.30%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.30%</t>
+          <t>6.03%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.66%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>15,779,000</t>
+          <t>16,333,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>5.48%</t>
         </is>
       </c>
     </row>
@@ -770,73 +770,73 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.94%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,191,000</t>
+          <t>2,417,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.46%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,417,000</t>
+          <t>9,231,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>4.36%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>9,149,000</t>
+          <t>5,191,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>4.29%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>14,770,000</t>
+          <t>15,139,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.77%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.55%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
@@ -1298,46 +1298,46 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1364,19 +1364,19 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>4,510,225,108</t>
+          <t>5,703,284,932</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-2,837,476,642</t>
+          <t>-3,322,852,533</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
